--- a/docs/03_external_design.xlsx
+++ b/docs/03_external_design.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9397,6 +9397,28 @@
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Prototype translated to English (v21): new screenshots, English on-screen labels, message list without Portuguese column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>DLG-02 and DLG-04 screenshots: noetic_runtime renamed noetic (crate merge, Basic Design 0.3).</t>
         </is>
       </c>
     </row>

--- a/docs/03_external_design.xlsx
+++ b/docs/03_external_design.xlsx
@@ -1355,11 +1355,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>外部設計書</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>External Design (外部設計書)</t>
+          <t>External Design</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1389,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1449,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Requirements Definition (要件定義) · Basic Design (基本設計書) · Detailed Design (詳細設計書, to be written) · Clickable prototype v20</t>
+          <t>Requirements Definition · Basic Design · Detailed Design (to be written) · Clickable prototype v20</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9419,6 +9415,28 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>DLG-02 and DLG-04 screenshots: noetic_runtime renamed noetic (crate merge, Basic Design 0.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Japanese names removed; the documents are in English only.</t>
         </is>
       </c>
     </row>

--- a/docs/03_external_design.xlsx
+++ b/docs/03_external_design.xlsx
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Screenshot SCR-04a — Steps of the activity "Pastar"  (items 1–5)</t>
+          <t>Screenshot SCR-04a — Steps of the activity "Graze"  (items 1–5)</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Apagar passo</t>
+          <t>Delete step</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Clique num animal · …</t>
+          <t>Click an animal · …</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>1 dia = 5 min</t>
+          <t>1 day = 5 min</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Dar sede, Dar fome, Cansar, Acalmar, Ferir, Curar, Barulho perto, Assustar — change the live animal to see its reaction.</t>
+          <t>Make thirsty, Make hungry, Tire, Calm, Injure, Heal, Noise nearby, Scare — change the live animal to see its reaction.</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Shows the planned path.</t>
+          <t>Shows a line to the current movement target.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -8177,7 +8177,7 @@
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Species tabs → Modelo 3D</t>
+          <t>Species tabs → 3D Model</t>
         </is>
       </c>
       <c r="D7" s="15" t="n"/>
@@ -9287,7 +9287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9437,6 +9437,28 @@
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Japanese names removed; the documents are in English only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>English UI leftovers: Graze, Type, Delete step, Click an animal, 1 day = 5 min, quick-test buttons, 3D Model, Copy. SCR-08-03 shows the line to the movement target (no path planner).</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11040,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Copiar</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -12234,7 +12256,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Copiar</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -15897,7 +15919,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Species tabs → Modelo 3D</t>
+          <t>Species tabs → 3D Model</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">

--- a/docs/03_external_design.xlsx
+++ b/docs/03_external_design.xlsx
@@ -483,7 +483,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7086600" cy="5448300"/>
+    <ext cx="7086600" cy="5391150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t xml:space="preserve">0.10</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Requirements Definition · Basic Design · Detailed Design (to be written) · Clickable prototype v20</t>
+          <t xml:space="preserve">Requirements Definition · Basic Design · Internal Design · Detailed Design · Clickable prototype v21</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,11 @@
           <t>Removes the step and reconnects its neighbours.</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undo available (toast).</t>
+        </is>
+      </c>
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -4653,7 +4657,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Drag items to move; handles resize.</t>
+          <t xml:space="preserve">Drag items or river points to move; handles resize.</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -4695,7 +4699,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Tree, Bush, Rock, Burrow, Lake, Mud, Tall grass, Clover</t>
+          <t xml:space="preserve">Tree, Bush, Rock, Burrow, Pond, Mud, Tall grass, Clover</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -7170,12 +7174,12 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Hunger, Thirst, Fatigue</t>
+          <t xml:space="preserve">Hunger, Thirst, Fatigue</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>How fast each need rises per game hour.</t>
+          <t xml:space="preserve">How fast hunger, thirst and fatigue rise per game hour; the other needs follow their driver.</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -7326,7 +7330,7 @@
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>1–30 chars</t>
+          <t xml:space="preserve">1–40 chars (UI-07)</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -8774,7 +8778,11 @@
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1–40 chars (UI-07)</t>
+        </is>
+      </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
           <t>FR-401</t>
@@ -9287,7 +9295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9459,6 +9467,94 @@
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>English UI leftovers: Graze, Type, Delete step, Click an animal, 1 day = 5 min, quick-test buttons, 3D Model, Copy. SCR-08-03 shows the line to the movement target (no path planner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>FIO-04 saves the individuals with the project (Basic Design 0.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review against the other documents: SCR-02-08 calls the new API-BRN-026 create_activity; MSG-013 carries the reason (line and column); new MSG-023…030 for refused connections, newer files, save, load and copy failures, bad names and re-roll; MSG-009 no longer covers presets (MSG-016 does); one name rule (UI-07, SCR-10-09); Pond instead of Lake, and river points move with SCR-07-01; brain logo (SCR-01-02); cover cites prototype v21 and the Internal Design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each document checked against itself: DLG-02 gets a Save… button (DLG-02-04, API-IO-007) and Copy only copies; MSG-025 is for import only; MSG-029 asks uniqueness only where UI-07 does; MSG-016 on SCR-10 only; deleting a reaction or a step shows MSG-009 with Undo (UI-04); KEY-11 also on SCR-04; Area bar › Species opens the last species tab; Fear is no longer a driving need (SCR-03-12) and every need has its own rate slider (SCR-10-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Need rates are back to hunger, thirst and fatigue (SCR-10-06); fear and curiosity drive activities again (SCR-03-12); new MSG-031 for import fixes and KEY-12 Ctrl+Shift+Z redo; MSG-008, 009, 016 and 020 say exactly when they show; name ranges follow UI-07 (SCR-03-09, DLG-01-01, SCR-13-01); SCR-04-09 has Undo; SCR-01-14 opens the last species tab; FIO-02 and FIO-04 complete; transitions add SCR-03 → SCR-04 and the tree menu → DLG-01 and DLG-02; the DLG-02 screenshot counts 4 items.</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10404,7 @@
       <c r="H46" s="4" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Required, unique</t>
+          <t xml:space="preserve">Required, unique, 1–40 chars (UI-07)</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -10685,7 +10781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10830,7 +10926,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Screenshot DLG-02 — Export  (items 1–3)</t>
+          <t xml:space="preserve">Screenshot DLG-02 — Export  (items 1–4)</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11141,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Copies to clipboard (desktop: save dialog).</t>
+          <t xml:space="preserve">Copies the file to the clipboard.</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -11057,7 +11153,64 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>API-IO-006, API-IO-007</t>
+          <t xml:space="preserve">API-IO-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-02-04</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">btnSaveRon</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Button</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Save</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Save…</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opens a save dialog for the file.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FR-601</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-IO-007</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13543,12 +13696,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Branch % edited</t>
+          <t xml:space="preserve">Branch % edited, or a connection added to a branching block</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>SCR-03</t>
+          <t xml:space="preserve">SCR-02, SCR-03</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -13575,7 +13728,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Delete species/activity/folder/preset/terrain</t>
+          <t xml:space="preserve">Delete species/activity/folder/reaction/step/terrain; remove an activity from a species</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -13698,12 +13851,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>This does not look like a Noetic species file (missing "NoeticSpecies" or the name).</t>
+          <t xml:space="preserve">This is not a valid Noetic species file: &lt;reason&gt;.</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Import parse error</t>
+          <t xml:space="preserve">Import parse or validation error; a parse error names the line and column</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -13804,7 +13957,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>SCR-10, SCR-13</t>
+          <t xml:space="preserve">SCR-10, SCR-13 (saved)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -13927,7 +14080,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Quick test buttons</t>
+          <t xml:space="preserve">Quick test buttons that set a need (Make thirsty, Make hungry, Tire)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -14002,6 +14155,294 @@
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Button in toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;from&gt; cannot connect to &lt;to&gt;.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connection refused by the block rules</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-02, SCR-04</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Info</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">These blocks are already connected.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connecting the same two blocks again</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-02, SCR-04</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="29" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This file was made by a newer Noetic (schema &lt;n&gt;). Update Noetic to open it.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import of a file with a newer schema_version (a project that is too new fails with MSG-027)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-03</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline in dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="29" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not save &lt;file&gt;: &lt;reason&gt;.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autosave (tries again on the next change) or saving an exported file fails</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not open &lt;file&gt;: &lt;reason&gt;. A new project was opened instead.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loading the project fails at start</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not copy. Select the text and press Ctrl+C.</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clipboard unavailable</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-02, DLG-05</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline in dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Names need 1–40 characters; species, activity, folder and preset names must also be unique.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Invalid name (UI-07); an empty preset name shows MSG-015 instead</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline at the field</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Info</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;n&gt; animals got new personalities.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-roll all</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-10</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSG-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warning</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed while importing: &lt;changes&gt;.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import normalised weights or clamped values</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-03</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inline in dialog</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14775,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Export .ron dialog — layout screenshot(s) and 3 item definitions</t>
+          <t xml:space="preserve">Export .ron dialog — layout screenshot(s) and 4 item definitions</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14813,7 +15254,29 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>SCR-02, Project panel</t>
+          <t xml:space="preserve">SCR-02, SCR-04, Project panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY-12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ctrl+Shift+Z</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Redo the last undone action</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
         </is>
       </c>
     </row>
@@ -14934,7 +15397,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Destructive actions (delete species, folder, activity, preset, terrain item, world clear/reset) show a toast with Undo and are also undone with Ctrl+Z.</t>
+          <t xml:space="preserve">Destructive actions (delete species, folder, activity, preset, reaction block, step, terrain item, world clear/reset) show a toast with Undo and are also undone with Ctrl+Z.</t>
         </is>
       </c>
     </row>
@@ -14985,7 +15448,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Names are required, trimmed, 1–40 characters, unique within their kind (species, activity, folder, preset).</t>
+          <t xml:space="preserve">Names are required, trimmed and 1–40 characters, animal names included; species, activity, folder and preset names are unique within their kind.</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15615,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>DLG-02. File name = species name in snake_case + ".noetic.ron". Content preview and copy; desktop build opens a save dialog.</t>
+          <t xml:space="preserve">DLG-02. File name = species name in snake_case + ".noetic.ron". Content preview, Copy (DLG-02-03) and Save… (DLG-02-04).</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15642,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>DLG-03. File picker or pasted text. Validates schema_version and required fields; errors MSG-013. A name clash creates "&lt;name&gt; (2)".</t>
+          <t xml:space="preserve">DLG-03. File picker or pasted text. Validates schema_version and required fields; errors MSG-013, a newer schema MSG-025, fixes MSG-031. A name clash creates "&lt;name&gt; (2)".</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15696,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Folders, species, activities, presets, world layout, settings. Autosave (see Basic Design).</t>
+          <t xml:space="preserve">Folders, species, activities, presets, world layout, individuals, settings, UI state. Autosave (see Basic Design).</t>
         </is>
       </c>
     </row>
@@ -16068,7 +16531,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -16319,7 +16782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16459,12 +16922,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t xml:space="preserve">SCR-09…12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Species — Body</t>
+          <t xml:space="preserve">Species (last tab)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -17136,30 +17599,126 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">SCR-03</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Block details</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open steps (›)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-04</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activity steps</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POP-01</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tree menu</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export .ron</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-02</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POP-01</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tree menu</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New species here</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLG-01</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New species</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>DLG-xx</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Any dialog</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Esc / × / Close</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Previous screen</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17507,7 +18066,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Lens-diaphragm logo and product name.</t>
+          <t xml:space="preserve">Brain logo and product name.</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -18116,7 +18675,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Click → SCR-09.</t>
+          <t xml:space="preserve">Click → SCR-09…12 (last tab).</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
@@ -19131,7 +19690,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>API-BRN-013, API-PRJ-003</t>
+          <t xml:space="preserve">API-BRN-026</t>
         </is>
       </c>
     </row>
@@ -20819,7 +21378,7 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Required, 1–40 chars</t>
+          <t xml:space="preserve">Required, unique, 1–40 chars (UI-07)</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -20962,7 +21521,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Need that drives the score (hunger, thirst, fatigue, fear, boredom, urge to mark/fight/sing…).</t>
+          <t xml:space="preserve">Need that drives the score (hunger, thirst, fatigue, fear, safety, company, curiosity, boredom, urge to mark/fight/sing…).</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
